--- a/InputData/elec/BBNPPTY/BAU Ban New Power Plants This Year.xlsx
+++ b/InputData/elec/BBNPPTY/BAU Ban New Power Plants This Year.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29929"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="30326"/>
   <workbookPr defaultThemeVersion="124226"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\OliviaAshmoore\Documents\Github Repos\state-eps-data\ND\elec\BBNPPTY\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{018574FC-2C87-42EA-84FF-0B99C0076A4F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{62D39700-91E2-48AE-81C6-23706C32B159}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-98" yWindow="-98" windowWidth="21795" windowHeight="12975" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="About" sheetId="1" r:id="rId1"/>
@@ -524,12 +524,12 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:C24"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="2" max="2" width="60.86328125" customWidth="1"/>
+    <col min="2" max="2" width="60.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>27</v>
       </c>
@@ -537,10 +537,10 @@
         <v>43</v>
       </c>
       <c r="C1" s="3">
-        <v>46184</v>
-      </c>
-    </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.45">
+        <v>46261</v>
+      </c>
+    </row>
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>0</v>
       </c>
@@ -548,77 +548,77 @@
         <v>36</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="1" t="s">
         <v>17</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>28</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>41</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>29</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>31</v>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>42</v>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>35</v>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>32</v>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>33</v>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>37</v>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>40</v>
       </c>
@@ -635,12 +635,12 @@
     <tabColor theme="3"/>
   </sheetPr>
   <dimension ref="A1:AB25"/>
-  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="26.3984375" customWidth="1"/>
+    <col min="1" max="1" width="26.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>6</v>
       </c>
@@ -726,7 +726,7 @@
         <v>2050</v>
       </c>
     </row>
-    <row r="2" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>11</v>
       </c>
@@ -812,7 +812,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -898,7 +898,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>19</v>
       </c>
@@ -984,7 +984,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>5</v>
       </c>
@@ -1070,7 +1070,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>1</v>
       </c>
@@ -1156,7 +1156,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>12</v>
       </c>
@@ -1242,7 +1242,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>3</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>4</v>
       </c>
@@ -1414,7 +1414,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>2</v>
       </c>
@@ -1425,82 +1425,82 @@
         <v>1</v>
       </c>
       <c r="D10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA10">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:28" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="11" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>7</v>
       </c>
@@ -1511,19 +1511,19 @@
         <v>1</v>
       </c>
       <c r="D11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H11">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I11">
         <v>0</v>
@@ -1586,7 +1586,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A12" t="s">
         <v>8</v>
       </c>
@@ -1597,82 +1597,82 @@
         <v>1</v>
       </c>
       <c r="D12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="E12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="F12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="G12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="H12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="I12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="J12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="K12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="L12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="M12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="N12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="O12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="P12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Q12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="R12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="S12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="T12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="U12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="V12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="W12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="X12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Y12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="Z12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AA12">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="AB12">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="13" spans="1:28" x14ac:dyDescent="0.45">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="13" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A13" t="s">
         <v>9</v>
       </c>
@@ -1758,7 +1758,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="14" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A14" t="s">
         <v>10</v>
       </c>
@@ -1844,7 +1844,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="15" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A15" t="s">
         <v>13</v>
       </c>
@@ -1930,7 +1930,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="16" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A16" t="s">
         <v>14</v>
       </c>
@@ -2016,7 +2016,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="17" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="17" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A17" t="s">
         <v>15</v>
       </c>
@@ -2102,7 +2102,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="18" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="18" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A18" t="s">
         <v>16</v>
       </c>
@@ -2188,7 +2188,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="19" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="19" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A19" t="s">
         <v>20</v>
       </c>
@@ -2274,7 +2274,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="20" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="20" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A20" t="s">
         <v>21</v>
       </c>
@@ -2360,7 +2360,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="21" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="21" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A21" t="s">
         <v>22</v>
       </c>
@@ -2446,7 +2446,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="22" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="22" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A22" t="s">
         <v>23</v>
       </c>
@@ -2532,7 +2532,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="23" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="23" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A23" t="s">
         <v>24</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="24" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="24" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A24" t="s">
         <v>25</v>
       </c>
@@ -2704,7 +2704,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="25" spans="1:28" x14ac:dyDescent="0.45">
+    <row r="25" spans="1:28" x14ac:dyDescent="0.25">
       <c r="A25" t="s">
         <v>26</v>
       </c>
